--- a/tests/fixtures/test_cases/c101_fail_all.xlsx
+++ b/tests/fixtures/test_cases/c101_fail_all.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="chart_fail" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="chart1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -136,7 +136,7 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
-              <a:t>Title with ^superscript</a:t>
+              <a:t>Test Chart^1</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -151,7 +151,7 @@
           <order val="0"/>
           <tx>
             <strRef>
-              <f>'chart_fail'!B1</f>
+              <f>'chart1'!B1</f>
             </strRef>
           </tx>
           <spPr>
@@ -161,12 +161,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'chart_fail'!$A$2:$A$5</f>
+              <f>'chart1'!$A$2:$A$4</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'chart_fail'!$B$2:$B$5</f>
+              <f>'chart1'!$B$2:$B$4</f>
             </numRef>
           </val>
         </ser>
@@ -175,7 +175,7 @@
           <order val="1"/>
           <tx>
             <strRef>
-              <f>'chart_fail'!C1</f>
+              <f>'chart1'!C1</f>
             </strRef>
           </tx>
           <spPr>
@@ -185,12 +185,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'chart_fail'!$A$2:$A$5</f>
+              <f>'chart1'!$A$2:$A$4</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'chart_fail'!$C$2:$C$5</f>
+              <f>'chart1'!$C$2:$C$4</f>
             </numRef>
           </val>
         </ser>
@@ -199,7 +199,7 @@
           <order val="2"/>
           <tx>
             <strRef>
-              <f>'chart_fail'!D1</f>
+              <f>'chart1'!D1</f>
             </strRef>
           </tx>
           <spPr>
@@ -209,12 +209,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'chart_fail'!$A$2:$A$5</f>
+              <f>'chart1'!$A$2:$A$4</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'chart_fail'!$D$2:$D$5</f>
+              <f>'chart1'!$D$2:$D$4</f>
             </numRef>
           </val>
         </ser>
@@ -223,7 +223,7 @@
           <order val="3"/>
           <tx>
             <strRef>
-              <f>'chart_fail'!E1</f>
+              <f>'chart1'!E1</f>
             </strRef>
           </tx>
           <spPr>
@@ -233,12 +233,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'chart_fail'!$A$2:$A$5</f>
+              <f>'chart1'!$A$2:$A$4</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'chart_fail'!$E$2:$E$5</f>
+              <f>'chart1'!$E$2:$E$4</f>
             </numRef>
           </val>
         </ser>
@@ -247,7 +247,7 @@
           <order val="4"/>
           <tx>
             <strRef>
-              <f>'chart_fail'!F1</f>
+              <f>'chart1'!F1</f>
             </strRef>
           </tx>
           <spPr>
@@ -257,12 +257,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'chart_fail'!$A$2:$A$5</f>
+              <f>'chart1'!$A$2:$A$4</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'chart_fail'!$F$2:$F$5</f>
+              <f>'chart1'!$F$2:$F$4</f>
             </numRef>
           </val>
         </ser>
@@ -271,7 +271,7 @@
           <order val="5"/>
           <tx>
             <strRef>
-              <f>'chart_fail'!G1</f>
+              <f>'chart1'!G1</f>
             </strRef>
           </tx>
           <spPr>
@@ -281,12 +281,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'chart_fail'!$A$2:$A$5</f>
+              <f>'chart1'!$A$2:$A$4</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'chart_fail'!$G$2:$G$5</f>
+              <f>'chart1'!$G$2:$G$4</f>
             </numRef>
           </val>
         </ser>
@@ -295,7 +295,7 @@
           <order val="6"/>
           <tx>
             <strRef>
-              <f>'chart_fail'!H1</f>
+              <f>'chart1'!H1</f>
             </strRef>
           </tx>
           <spPr>
@@ -305,21 +305,99 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'chart_fail'!$A$2:$A$5</f>
+              <f>'chart1'!$A$2:$A$4</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'chart_fail'!$H$2:$H$5</f>
+              <f>'chart1'!$H$2:$H$4</f>
             </numRef>
           </val>
         </ser>
+        <dLbls>
+          <showVal val="1"/>
+        </dLbls>
+        <gapWidth val="150"/>
+        <axId val="10"/>
+        <axId val="100"/>
+      </barChart>
+      <catAx>
+        <axId val="10"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <delete val="0"/>
+        <axPos val="l"/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="100"/>
+        <lblOffset val="100"/>
+      </catAx>
+      <valAx>
+        <axId val="100"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <delete val="0"/>
+        <axPos val="l"/>
+        <majorGridlines/>
+        <title>
+          <tx>
+            <rich>
+              <a:bodyPr/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:t>Value (percent)</a:t>
+                </a:r>
+              </a:p>
+            </rich>
+          </tx>
+        </title>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="10"/>
+      </valAx>
+    </plotArea>
+    <legend>
+      <legendPos val="r"/>
+    </legend>
+    <plotVisOnly val="1"/>
+    <dispBlanksAs val="gap"/>
+  </chart>
+</chartSpace>
+</file>
+
+<file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
+<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <chart>
+    <title>
+      <tx>
+        <rich>
+          <a:bodyPr/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:t>Chart 2</a:t>
+            </a:r>
+          </a:p>
+        </rich>
+      </tx>
+    </title>
+    <plotArea>
+      <barChart>
+        <barDir val="col"/>
+        <grouping val="clustered"/>
         <ser>
-          <idx val="7"/>
-          <order val="7"/>
+          <idx val="0"/>
+          <order val="0"/>
           <tx>
             <strRef>
-              <f>'chart_fail'!I1</f>
+              <f>'chart1'!B12</f>
             </strRef>
           </tx>
           <spPr>
@@ -329,12 +407,84 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'chart_fail'!$A$2:$A$5</f>
+              <f>'chart1'!$A$13:$A$15</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'chart_fail'!$I$2:$I$5</f>
+              <f>'chart1'!$B$13:$B$15</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="1"/>
+          <order val="1"/>
+          <tx>
+            <strRef>
+              <f>'chart1'!C12</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'chart1'!$A$13:$A$15</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'chart1'!$C$13:$C$15</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="2"/>
+          <order val="2"/>
+          <tx>
+            <strRef>
+              <f>'chart1'!D12</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'chart1'!$A$13:$A$15</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'chart1'!$D$13:$D$15</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="3"/>
+          <order val="3"/>
+          <tx>
+            <strRef>
+              <f>'chart1'!E12</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'chart1'!$A$13:$A$15</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'chart1'!$E$13:$E$15</f>
             </numRef>
           </val>
         </ser>
@@ -380,10 +530,10 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>7</row>
+      <row>5</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="7200000" cy="3600000"/>
+    <ext cx="5400000" cy="2880000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="1" name="Chart 1"/>
@@ -393,6 +543,28 @@
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
           <c:chart r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </graphicFrame>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>5</col>
+      <colOff>0</colOff>
+      <row>5</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="5400000" cy="2700000"/>
+    <graphicFrame>
+      <nvGraphicFramePr>
+        <cNvPr id="2" name="Chart 2"/>
+        <cNvGraphicFramePr/>
+      </nvGraphicFramePr>
+      <xfrm/>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart r:id="rId2"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -690,7 +862,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I5"/>
+  <dimension ref="A1:H15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -734,11 +906,6 @@
           <t>S7</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>S8</t>
-        </is>
-      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -749,9 +916,7 @@
       <c r="B2" t="n">
         <v>4</v>
       </c>
-      <c r="C2" t="n">
-        <v>6</v>
-      </c>
+      <c r="C2" t="inlineStr"/>
       <c r="D2" t="n">
         <v>8</v>
       </c>
@@ -766,9 +931,6 @@
       </c>
       <c r="H2" t="n">
         <v>16</v>
-      </c>
-      <c r="I2" t="n">
-        <v>18</v>
       </c>
     </row>
     <row r="3">
@@ -798,9 +960,6 @@
       <c r="H3" t="n">
         <v>24</v>
       </c>
-      <c r="I3" t="n">
-        <v>27</v>
-      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -829,39 +988,92 @@
       <c r="H4" t="n">
         <v>32</v>
       </c>
-      <c r="I4" t="n">
-        <v>36</v>
-      </c>
     </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>R5</t>
-        </is>
-      </c>
-      <c r="B5" t="n">
-        <v>10</v>
-      </c>
-      <c r="C5" t="n">
-        <v>15</v>
-      </c>
-      <c r="D5" t="n">
-        <v>20</v>
-      </c>
-      <c r="E5" t="n">
-        <v>25</v>
-      </c>
-      <c r="F5" t="n">
+    <row r="10">
+      <c r="A10" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Cat</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>V1</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>V2</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>V3</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>V4</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>R13</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>26</v>
+      </c>
+      <c r="C13" t="n">
+        <v>39</v>
+      </c>
+      <c r="D13" t="n">
+        <v>52</v>
+      </c>
+      <c r="E13" t="n">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>R14</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>28</v>
+      </c>
+      <c r="C14" t="n">
+        <v>42</v>
+      </c>
+      <c r="D14" t="n">
+        <v>56</v>
+      </c>
+      <c r="E14" t="n">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>R15</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
         <v>30</v>
       </c>
-      <c r="G5" t="n">
-        <v>35</v>
-      </c>
-      <c r="H5" t="n">
-        <v>40</v>
-      </c>
-      <c r="I5" t="n">
+      <c r="C15" t="n">
         <v>45</v>
+      </c>
+      <c r="D15" t="n">
+        <v>60</v>
+      </c>
+      <c r="E15" t="n">
+        <v>75</v>
       </c>
     </row>
   </sheetData>

--- a/tests/fixtures/test_cases/c101_fail_all.xlsx
+++ b/tests/fixtures/test_cases/c101_fail_all.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="chart1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="chart_fail" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -136,7 +136,7 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
-              <a:t>Test Chart^1</a:t>
+              <a:t>Title with ^superscript</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -151,7 +151,7 @@
           <order val="0"/>
           <tx>
             <strRef>
-              <f>'chart1'!B1</f>
+              <f>'chart_fail'!B1</f>
             </strRef>
           </tx>
           <spPr>
@@ -161,12 +161,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'chart1'!$A$2:$A$4</f>
+              <f>'chart_fail'!$A$2:$A$5</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'chart1'!$B$2:$B$4</f>
+              <f>'chart_fail'!$B$2:$B$5</f>
             </numRef>
           </val>
         </ser>
@@ -175,7 +175,7 @@
           <order val="1"/>
           <tx>
             <strRef>
-              <f>'chart1'!C1</f>
+              <f>'chart_fail'!C1</f>
             </strRef>
           </tx>
           <spPr>
@@ -185,12 +185,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'chart1'!$A$2:$A$4</f>
+              <f>'chart_fail'!$A$2:$A$5</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'chart1'!$C$2:$C$4</f>
+              <f>'chart_fail'!$C$2:$C$5</f>
             </numRef>
           </val>
         </ser>
@@ -199,7 +199,7 @@
           <order val="2"/>
           <tx>
             <strRef>
-              <f>'chart1'!D1</f>
+              <f>'chart_fail'!D1</f>
             </strRef>
           </tx>
           <spPr>
@@ -209,12 +209,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'chart1'!$A$2:$A$4</f>
+              <f>'chart_fail'!$A$2:$A$5</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'chart1'!$D$2:$D$4</f>
+              <f>'chart_fail'!$D$2:$D$5</f>
             </numRef>
           </val>
         </ser>
@@ -223,7 +223,7 @@
           <order val="3"/>
           <tx>
             <strRef>
-              <f>'chart1'!E1</f>
+              <f>'chart_fail'!E1</f>
             </strRef>
           </tx>
           <spPr>
@@ -233,12 +233,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'chart1'!$A$2:$A$4</f>
+              <f>'chart_fail'!$A$2:$A$5</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'chart1'!$E$2:$E$4</f>
+              <f>'chart_fail'!$E$2:$E$5</f>
             </numRef>
           </val>
         </ser>
@@ -247,7 +247,7 @@
           <order val="4"/>
           <tx>
             <strRef>
-              <f>'chart1'!F1</f>
+              <f>'chart_fail'!F1</f>
             </strRef>
           </tx>
           <spPr>
@@ -257,12 +257,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'chart1'!$A$2:$A$4</f>
+              <f>'chart_fail'!$A$2:$A$5</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'chart1'!$F$2:$F$4</f>
+              <f>'chart_fail'!$F$2:$F$5</f>
             </numRef>
           </val>
         </ser>
@@ -271,7 +271,7 @@
           <order val="5"/>
           <tx>
             <strRef>
-              <f>'chart1'!G1</f>
+              <f>'chart_fail'!G1</f>
             </strRef>
           </tx>
           <spPr>
@@ -281,12 +281,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'chart1'!$A$2:$A$4</f>
+              <f>'chart_fail'!$A$2:$A$5</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'chart1'!$G$2:$G$4</f>
+              <f>'chart_fail'!$G$2:$G$5</f>
             </numRef>
           </val>
         </ser>
@@ -295,7 +295,7 @@
           <order val="6"/>
           <tx>
             <strRef>
-              <f>'chart1'!H1</f>
+              <f>'chart_fail'!H1</f>
             </strRef>
           </tx>
           <spPr>
@@ -305,99 +305,21 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'chart1'!$A$2:$A$4</f>
+              <f>'chart_fail'!$A$2:$A$5</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'chart1'!$H$2:$H$4</f>
+              <f>'chart_fail'!$H$2:$H$5</f>
             </numRef>
           </val>
         </ser>
-        <dLbls>
-          <showVal val="1"/>
-        </dLbls>
-        <gapWidth val="150"/>
-        <axId val="10"/>
-        <axId val="100"/>
-      </barChart>
-      <catAx>
-        <axId val="10"/>
-        <scaling>
-          <orientation val="minMax"/>
-        </scaling>
-        <delete val="0"/>
-        <axPos val="l"/>
-        <majorTickMark val="none"/>
-        <minorTickMark val="none"/>
-        <crossAx val="100"/>
-        <lblOffset val="100"/>
-      </catAx>
-      <valAx>
-        <axId val="100"/>
-        <scaling>
-          <orientation val="minMax"/>
-        </scaling>
-        <delete val="0"/>
-        <axPos val="l"/>
-        <majorGridlines/>
-        <title>
-          <tx>
-            <rich>
-              <a:bodyPr/>
-              <a:p>
-                <a:pPr>
-                  <a:defRPr/>
-                </a:pPr>
-                <a:r>
-                  <a:t>Value (percent)</a:t>
-                </a:r>
-              </a:p>
-            </rich>
-          </tx>
-        </title>
-        <majorTickMark val="none"/>
-        <minorTickMark val="none"/>
-        <crossAx val="10"/>
-      </valAx>
-    </plotArea>
-    <legend>
-      <legendPos val="r"/>
-    </legend>
-    <plotVisOnly val="1"/>
-    <dispBlanksAs val="gap"/>
-  </chart>
-</chartSpace>
-</file>
-
-<file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
-  <chart>
-    <title>
-      <tx>
-        <rich>
-          <a:bodyPr/>
-          <a:p>
-            <a:pPr>
-              <a:defRPr/>
-            </a:pPr>
-            <a:r>
-              <a:t>Chart 2</a:t>
-            </a:r>
-          </a:p>
-        </rich>
-      </tx>
-    </title>
-    <plotArea>
-      <barChart>
-        <barDir val="col"/>
-        <grouping val="clustered"/>
         <ser>
-          <idx val="0"/>
-          <order val="0"/>
+          <idx val="7"/>
+          <order val="7"/>
           <tx>
             <strRef>
-              <f>'chart1'!B12</f>
+              <f>'chart_fail'!I1</f>
             </strRef>
           </tx>
           <spPr>
@@ -407,84 +329,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'chart1'!$A$13:$A$15</f>
+              <f>'chart_fail'!$A$2:$A$5</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'chart1'!$B$13:$B$15</f>
-            </numRef>
-          </val>
-        </ser>
-        <ser>
-          <idx val="1"/>
-          <order val="1"/>
-          <tx>
-            <strRef>
-              <f>'chart1'!C12</f>
-            </strRef>
-          </tx>
-          <spPr>
-            <a:ln>
-              <a:prstDash val="solid"/>
-            </a:ln>
-          </spPr>
-          <cat>
-            <numRef>
-              <f>'chart1'!$A$13:$A$15</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'chart1'!$C$13:$C$15</f>
-            </numRef>
-          </val>
-        </ser>
-        <ser>
-          <idx val="2"/>
-          <order val="2"/>
-          <tx>
-            <strRef>
-              <f>'chart1'!D12</f>
-            </strRef>
-          </tx>
-          <spPr>
-            <a:ln>
-              <a:prstDash val="solid"/>
-            </a:ln>
-          </spPr>
-          <cat>
-            <numRef>
-              <f>'chart1'!$A$13:$A$15</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'chart1'!$D$13:$D$15</f>
-            </numRef>
-          </val>
-        </ser>
-        <ser>
-          <idx val="3"/>
-          <order val="3"/>
-          <tx>
-            <strRef>
-              <f>'chart1'!E12</f>
-            </strRef>
-          </tx>
-          <spPr>
-            <a:ln>
-              <a:prstDash val="solid"/>
-            </a:ln>
-          </spPr>
-          <cat>
-            <numRef>
-              <f>'chart1'!$A$13:$A$15</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'chart1'!$E$13:$E$15</f>
+              <f>'chart_fail'!$I$2:$I$5</f>
             </numRef>
           </val>
         </ser>
@@ -530,10 +380,10 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>5</row>
+      <row>7</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="5400000" cy="2880000"/>
+    <ext cx="7200000" cy="3600000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="1" name="Chart 1"/>
@@ -543,28 +393,6 @@
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
           <c:chart r:id="rId1"/>
-        </a:graphicData>
-      </a:graphic>
-    </graphicFrame>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>5</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="5400000" cy="2700000"/>
-    <graphicFrame>
-      <nvGraphicFramePr>
-        <cNvPr id="2" name="Chart 2"/>
-        <cNvGraphicFramePr/>
-      </nvGraphicFramePr>
-      <xfrm/>
-      <a:graphic>
-        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart r:id="rId2"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -862,7 +690,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H15"/>
+  <dimension ref="A1:I5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -906,6 +734,11 @@
           <t>S7</t>
         </is>
       </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>S8</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -916,7 +749,9 @@
       <c r="B2" t="n">
         <v>4</v>
       </c>
-      <c r="C2" t="inlineStr"/>
+      <c r="C2" t="n">
+        <v>6</v>
+      </c>
       <c r="D2" t="n">
         <v>8</v>
       </c>
@@ -931,6 +766,9 @@
       </c>
       <c r="H2" t="n">
         <v>16</v>
+      </c>
+      <c r="I2" t="n">
+        <v>18</v>
       </c>
     </row>
     <row r="3">
@@ -960,6 +798,9 @@
       <c r="H3" t="n">
         <v>24</v>
       </c>
+      <c r="I3" t="n">
+        <v>27</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -988,92 +829,39 @@
       <c r="H4" t="n">
         <v>32</v>
       </c>
+      <c r="I4" t="n">
+        <v>36</v>
+      </c>
     </row>
-    <row r="10">
-      <c r="A10" t="inlineStr"/>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>Cat</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>V1</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>V2</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>V3</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>V4</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>R13</t>
-        </is>
-      </c>
-      <c r="B13" t="n">
-        <v>26</v>
-      </c>
-      <c r="C13" t="n">
-        <v>39</v>
-      </c>
-      <c r="D13" t="n">
-        <v>52</v>
-      </c>
-      <c r="E13" t="n">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>R14</t>
-        </is>
-      </c>
-      <c r="B14" t="n">
-        <v>28</v>
-      </c>
-      <c r="C14" t="n">
-        <v>42</v>
-      </c>
-      <c r="D14" t="n">
-        <v>56</v>
-      </c>
-      <c r="E14" t="n">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>R15</t>
-        </is>
-      </c>
-      <c r="B15" t="n">
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>R5</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>10</v>
+      </c>
+      <c r="C5" t="n">
+        <v>15</v>
+      </c>
+      <c r="D5" t="n">
+        <v>20</v>
+      </c>
+      <c r="E5" t="n">
+        <v>25</v>
+      </c>
+      <c r="F5" t="n">
         <v>30</v>
       </c>
-      <c r="C15" t="n">
+      <c r="G5" t="n">
+        <v>35</v>
+      </c>
+      <c r="H5" t="n">
+        <v>40</v>
+      </c>
+      <c r="I5" t="n">
         <v>45</v>
-      </c>
-      <c r="D15" t="n">
-        <v>60</v>
-      </c>
-      <c r="E15" t="n">
-        <v>75</v>
       </c>
     </row>
   </sheetData>

--- a/tests/fixtures/test_cases/c101_fail_all.xlsx
+++ b/tests/fixtures/test_cases/c101_fail_all.xlsx
@@ -777,9 +777,6 @@
           <t>R3</t>
         </is>
       </c>
-      <c r="B3" t="n">
-        <v>6</v>
-      </c>
       <c r="C3" t="n">
         <v>9</v>
       </c>
